--- a/pregenereated_results/s2/ate_iptw_gee_IPTW_GEE_turnover_intention_index_mgr.xlsx
+++ b/pregenereated_results/s2/ate_iptw_gee_IPTW_GEE_turnover_intention_index_mgr.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Covariate_Balance" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Weight_Diagnostics" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ATE_MSM" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Propensity_Model" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Covariate_Balance" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Weight_Diagnostics" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="ATE_MSM" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Propensity_Model" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G32"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -483,10 +483,10 @@
         <v>-0.019</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.006</v>
+        <v>-0.004</v>
       </c>
       <c r="E2" t="n">
-        <v>0.013</v>
+        <v>0.015</v>
       </c>
       <c r="F2" t="b">
         <v>1</v>
@@ -525,7 +525,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>team_size</t>
+          <t>num_direct_reports</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -534,13 +534,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>-0.045</v>
+        <v>0.012</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.03</v>
+        <v>-0.014</v>
       </c>
       <c r="E4" t="n">
-        <v>0.015</v>
+        <v>-0.002</v>
       </c>
       <c r="F4" t="b">
         <v>1</v>
@@ -552,22 +552,22 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>is_new_manager</t>
+          <t>tot_span_of_control</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>binary</t>
+          <t>continuous</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.097</v>
+        <v>0.046</v>
       </c>
       <c r="D5" t="n">
-        <v>0.024</v>
+        <v>0.011</v>
       </c>
       <c r="E5" t="n">
-        <v>0.07300000000000001</v>
+        <v>0.035</v>
       </c>
       <c r="F5" t="b">
         <v>1</v>
@@ -579,22 +579,22 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>gender_Male</t>
+          <t>is_new_manager</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>categorical</t>
+          <t>binary</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>-0.024</v>
+        <v>0.097</v>
       </c>
       <c r="D6" t="n">
-        <v>0.027</v>
+        <v>0.021</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.002999999999999999</v>
+        <v>0.076</v>
       </c>
       <c r="F6" t="b">
         <v>1</v>
@@ -606,7 +606,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>gender_Non_Binary_Other</t>
+          <t>gender_Male</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -615,13 +615,13 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.046</v>
+        <v>-0.024</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.001</v>
+        <v>0.027</v>
       </c>
       <c r="E7" t="n">
-        <v>0.045</v>
+        <v>-0.002999999999999999</v>
       </c>
       <c r="F7" t="b">
         <v>1</v>
@@ -633,7 +633,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>job_family_Communications</t>
+          <t>gender_Non_Binary_Other</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -642,13 +642,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>-0.008999999999999999</v>
+        <v>0.046</v>
       </c>
       <c r="D8" t="n">
-        <v>0.002</v>
+        <v>-0.002</v>
       </c>
       <c r="E8" t="n">
-        <v>0.006999999999999999</v>
+        <v>0.044</v>
       </c>
       <c r="F8" t="b">
         <v>1</v>
@@ -660,7 +660,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>job_family_Data_Science</t>
+          <t>job_family_Communications</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -669,13 +669,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>-0.074</v>
+        <v>-0.008999999999999999</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.042</v>
+        <v>-0.001</v>
       </c>
       <c r="E9" t="n">
-        <v>0.03199999999999999</v>
+        <v>0.008</v>
       </c>
       <c r="F9" t="b">
         <v>1</v>
@@ -687,7 +687,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>job_family_Finance_and_Accounting</t>
+          <t>job_family_Data_Science</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -696,13 +696,13 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.034</v>
+        <v>-0.074</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.007</v>
+        <v>-0.042</v>
       </c>
       <c r="E10" t="n">
-        <v>0.027</v>
+        <v>0.03199999999999999</v>
       </c>
       <c r="F10" t="b">
         <v>1</v>
@@ -714,7 +714,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>job_family_Human_Resources</t>
+          <t>job_family_Finance_and_Accounting</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -723,13 +723,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.023</v>
+        <v>0.034</v>
       </c>
       <c r="D11" t="n">
-        <v>0.011</v>
+        <v>-0.008</v>
       </c>
       <c r="E11" t="n">
-        <v>0.012</v>
+        <v>0.026</v>
       </c>
       <c r="F11" t="b">
         <v>1</v>
@@ -741,7 +741,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>job_family_IT_and_Digital</t>
+          <t>job_family_Human_Resources</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -750,13 +750,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.007</v>
+        <v>0.023</v>
       </c>
       <c r="D12" t="n">
-        <v>0.024</v>
+        <v>0.01</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.017</v>
+        <v>0.013</v>
       </c>
       <c r="F12" t="b">
         <v>1</v>
@@ -768,7 +768,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>job_family_Legal_and_Compliance</t>
+          <t>job_family_IT_and_Digital</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -777,13 +777,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.041</v>
+        <v>0.007</v>
       </c>
       <c r="D13" t="n">
-        <v>0.039</v>
+        <v>0.025</v>
       </c>
       <c r="E13" t="n">
-        <v>0.002000000000000002</v>
+        <v>-0.018</v>
       </c>
       <c r="F13" t="b">
         <v>1</v>
@@ -795,7 +795,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>job_family_Market_Access</t>
+          <t>job_family_Legal_and_Compliance</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -804,13 +804,13 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.005</v>
+        <v>0.041</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.012</v>
+        <v>0.038</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.007</v>
+        <v>0.003000000000000003</v>
       </c>
       <c r="F14" t="b">
         <v>1</v>
@@ -822,7 +822,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>job_family_Marketing</t>
+          <t>job_family_Market_Access</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -831,13 +831,13 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.032</v>
+        <v>0.005</v>
       </c>
       <c r="D15" t="n">
-        <v>0.035</v>
+        <v>-0.013</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.003000000000000003</v>
+        <v>-0.008</v>
       </c>
       <c r="F15" t="b">
         <v>1</v>
@@ -849,7 +849,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>job_family_Medical_Affairs</t>
+          <t>job_family_Marketing</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -858,13 +858,13 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>-0.014</v>
+        <v>0.032</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.006</v>
+        <v>0.03</v>
       </c>
       <c r="E16" t="n">
-        <v>0.008</v>
+        <v>0.002000000000000002</v>
       </c>
       <c r="F16" t="b">
         <v>1</v>
@@ -876,7 +876,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>job_family_Pharmacovigilance</t>
+          <t>job_family_Medical_Affairs</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -885,13 +885,13 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>-0</v>
+        <v>-0.014</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.008999999999999999</v>
+        <v>-0.003</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.008999999999999999</v>
+        <v>0.011</v>
       </c>
       <c r="F17" t="b">
         <v>1</v>
@@ -903,7 +903,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>job_family_Quality_Assurance</t>
+          <t>job_family_Pharmacovigilance</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -912,13 +912,13 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>-0.008</v>
+        <v>-0</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.001</v>
+        <v>-0.004</v>
       </c>
       <c r="E18" t="n">
-        <v>0.007</v>
+        <v>-0.004</v>
       </c>
       <c r="F18" t="b">
         <v>1</v>
@@ -930,7 +930,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>job_family_Regulatory_Affairs</t>
+          <t>job_family_Quality_Assurance</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -939,13 +939,13 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.077</v>
+        <v>-0.008</v>
       </c>
       <c r="D19" t="n">
-        <v>0.033</v>
+        <v>-0.001</v>
       </c>
       <c r="E19" t="n">
-        <v>0.044</v>
+        <v>0.007</v>
       </c>
       <c r="F19" t="b">
         <v>1</v>
@@ -957,7 +957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>job_family_Sales</t>
+          <t>job_family_Regulatory_Affairs</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -966,13 +966,13 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>-0.019</v>
+        <v>0.077</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.021</v>
+        <v>0.031</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.002000000000000002</v>
+        <v>0.046</v>
       </c>
       <c r="F20" t="b">
         <v>1</v>
@@ -984,7 +984,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>job_family_Supply_Chain</t>
+          <t>job_family_Sales</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -993,16 +993,16 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>-0.113</v>
+        <v>-0.019</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.055</v>
+        <v>-0.023</v>
       </c>
       <c r="E21" t="n">
-        <v>0.058</v>
+        <v>-0.004</v>
       </c>
       <c r="F21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G21" t="b">
         <v>1</v>
@@ -1011,7 +1011,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>organization_Digital</t>
+          <t>job_family_Supply_Chain</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1020,13 +1020,13 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.197</v>
+        <v>-0.113</v>
       </c>
       <c r="D22" t="n">
-        <v>0.068</v>
+        <v>-0.05</v>
       </c>
       <c r="E22" t="n">
-        <v>0.129</v>
+        <v>0.063</v>
       </c>
       <c r="F22" t="b">
         <v>0</v>
@@ -1038,7 +1038,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>organization_Finance</t>
+          <t>organization_Digital</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1047,13 +1047,13 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>-0.143</v>
+        <v>0.197</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.043</v>
+        <v>0.065</v>
       </c>
       <c r="E23" t="n">
-        <v>0.09999999999999999</v>
+        <v>0.132</v>
       </c>
       <c r="F23" t="b">
         <v>0</v>
@@ -1065,7 +1065,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>organization_HR</t>
+          <t>organization_Finance</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1074,16 +1074,16 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>-0.054</v>
+        <v>-0.143</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.026</v>
+        <v>-0.042</v>
       </c>
       <c r="E24" t="n">
-        <v>0.028</v>
+        <v>0.101</v>
       </c>
       <c r="F24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G24" t="b">
         <v>1</v>
@@ -1092,7 +1092,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>organization_Manufacturing</t>
+          <t>organization_HR</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1101,16 +1101,16 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>-0.128</v>
+        <v>-0.054</v>
       </c>
       <c r="D25" t="n">
-        <v>0.016</v>
+        <v>-0.027</v>
       </c>
       <c r="E25" t="n">
-        <v>0.112</v>
+        <v>0.027</v>
       </c>
       <c r="F25" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G25" t="b">
         <v>1</v>
@@ -1119,7 +1119,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>organization_RandD</t>
+          <t>organization_Manufacturing</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1128,13 +1128,13 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.227</v>
+        <v>-0.128</v>
       </c>
       <c r="D26" t="n">
-        <v>0.025</v>
+        <v>0.019</v>
       </c>
       <c r="E26" t="n">
-        <v>0.202</v>
+        <v>0.109</v>
       </c>
       <c r="F26" t="b">
         <v>0</v>
@@ -1146,7 +1146,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>performance_rating_Far_Exceeds</t>
+          <t>organization_RandD</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1155,13 +1155,13 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.392</v>
+        <v>0.227</v>
       </c>
       <c r="D27" t="n">
-        <v>0.032</v>
+        <v>0.022</v>
       </c>
       <c r="E27" t="n">
-        <v>0.36</v>
+        <v>0.205</v>
       </c>
       <c r="F27" t="b">
         <v>0</v>
@@ -1173,7 +1173,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>performance_rating_Meets</t>
+          <t>performance_rating_Far_Exceeds</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1182,13 +1182,13 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>-0.401</v>
+        <v>0.392</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.043</v>
+        <v>0.03</v>
       </c>
       <c r="E28" t="n">
-        <v>0.358</v>
+        <v>0.362</v>
       </c>
       <c r="F28" t="b">
         <v>0</v>
@@ -1200,7 +1200,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>region_Europe</t>
+          <t>performance_rating_Meets</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1209,13 +1209,13 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.107</v>
+        <v>-0.401</v>
       </c>
       <c r="D29" t="n">
-        <v>0.044</v>
+        <v>-0.038</v>
       </c>
       <c r="E29" t="n">
-        <v>0.063</v>
+        <v>0.363</v>
       </c>
       <c r="F29" t="b">
         <v>0</v>
@@ -1227,7 +1227,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>region_Latin_America</t>
+          <t>region_Europe</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1236,16 +1236,16 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>-0.041</v>
+        <v>0.107</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.011</v>
+        <v>0.042</v>
       </c>
       <c r="E30" t="n">
-        <v>0.03</v>
+        <v>0.065</v>
       </c>
       <c r="F30" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G30" t="b">
         <v>1</v>
@@ -1254,7 +1254,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>region_Middle_East_and_Africa</t>
+          <t>region_Latin_America</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1263,13 +1263,13 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>-0.066</v>
+        <v>-0.041</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.057</v>
+        <v>-0.013</v>
       </c>
       <c r="E31" t="n">
-        <v>0.009000000000000001</v>
+        <v>0.028</v>
       </c>
       <c r="F31" t="b">
         <v>1</v>
@@ -1281,27 +1281,54 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
+          <t>region_Middle_East_and_Africa</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>categorical</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>-0.066</v>
+      </c>
+      <c r="D32" t="n">
+        <v>-0.057</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.009000000000000001</v>
+      </c>
+      <c r="F32" t="b">
+        <v>1</v>
+      </c>
+      <c r="G32" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
           <t>region_North_America</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>categorical</t>
         </is>
       </c>
-      <c r="C32" t="n">
+      <c r="C33" t="n">
         <v>0.022</v>
       </c>
-      <c r="D32" t="n">
-        <v>0.014</v>
-      </c>
-      <c r="E32" t="n">
-        <v>0.007999999999999998</v>
-      </c>
-      <c r="F32" t="b">
-        <v>1</v>
-      </c>
-      <c r="G32" t="b">
+      <c r="D33" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.006999999999999999</v>
+      </c>
+      <c r="F33" t="b">
+        <v>1</v>
+      </c>
+      <c r="G33" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1361,22 +1388,22 @@
         <v>7220</v>
       </c>
       <c r="B2" t="n">
-        <v>7099.15044992504</v>
+        <v>7094.386718944054</v>
       </c>
       <c r="C2" t="n">
-        <v>0.9952614504155347</v>
+        <v>0.9957648995493169</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1298633463115101</v>
+        <v>0.1325095691671194</v>
       </c>
       <c r="E2" t="n">
-        <v>1.630560047471351</v>
+        <v>1.678870188120528</v>
       </c>
       <c r="F2" t="n">
-        <v>1.129699880048327</v>
+        <v>1.124267686541995</v>
       </c>
       <c r="G2" t="n">
-        <v>1.630026169528008</v>
+        <v>1.67804342107184</v>
       </c>
     </row>
   </sheetData>
@@ -1390,7 +1417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G35"/>
+  <dimension ref="A1:G36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1437,19 +1464,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.468792819720192</v>
+        <v>1.588437647332136</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1009406996877883</v>
+        <v>0.09951383604477247</v>
       </c>
       <c r="D2" t="n">
-        <v>1.270952683757853</v>
+        <v>1.393394112720958</v>
       </c>
       <c r="E2" t="n">
-        <v>1.66663295568253</v>
+        <v>1.783481181943314</v>
       </c>
       <c r="F2" t="n">
-        <v>5.751633793604918e-48</v>
+        <v>2.351594952938109e-57</v>
       </c>
       <c r="G2" t="n">
         <v>0.05</v>
@@ -1462,19 +1489,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.002198699402528395</v>
+        <v>0.002289543090502408</v>
       </c>
       <c r="C3" t="n">
-        <v>0.02007605165058946</v>
+        <v>0.0200435016019184</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.03714963878439285</v>
+        <v>-0.03699499817332853</v>
       </c>
       <c r="E3" t="n">
-        <v>0.04154703758944965</v>
+        <v>0.04157408435433335</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9127912357235334</v>
+        <v>0.9090565031154852</v>
       </c>
       <c r="G3" t="n">
         <v>0.05</v>
@@ -1487,19 +1514,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.02796854217734963</v>
+        <v>-0.02760529193760395</v>
       </c>
       <c r="C4" t="n">
-        <v>0.05296146174444206</v>
+        <v>0.0518165195556562</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.1317710997650519</v>
+        <v>-0.1291638040709055</v>
       </c>
       <c r="E4" t="n">
-        <v>0.07583401541035267</v>
+        <v>0.0739532201956976</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5974352482562559</v>
+        <v>0.5942060998044847</v>
       </c>
       <c r="G4" t="n">
         <v>0.05</v>
@@ -1512,19 +1539,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-7.020348029387889e-05</v>
+        <v>0.001979053634585209</v>
       </c>
       <c r="C5" t="n">
-        <v>0.03412441273797081</v>
+        <v>0.03523203519821221</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.06695282344029652</v>
+        <v>-0.06707446645595823</v>
       </c>
       <c r="E5" t="n">
-        <v>0.06681241647970876</v>
+        <v>0.07103257372512865</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9983585290109235</v>
+        <v>0.9552047922717004</v>
       </c>
       <c r="G5" t="n">
         <v>0.05</v>
@@ -1537,19 +1564,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0339391375339689</v>
+        <v>0.03340001985125</v>
       </c>
       <c r="C6" t="n">
-        <v>0.03403794642010514</v>
+        <v>0.0328625850817722</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.03277401155714123</v>
+        <v>-0.03100946334790678</v>
       </c>
       <c r="E6" t="n">
-        <v>0.100652286625079</v>
+        <v>0.09780950305040678</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3187173824129126</v>
+        <v>0.3094608416342981</v>
       </c>
       <c r="G6" t="n">
         <v>0.05</v>
@@ -1562,19 +1589,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-0.01613371243139131</v>
+        <v>-0.01514663535578092</v>
       </c>
       <c r="C7" t="n">
-        <v>0.033734140337232</v>
+        <v>0.03537760492293866</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.08225141254178589</v>
+        <v>-0.08448546686402761</v>
       </c>
       <c r="E7" t="n">
-        <v>0.04998398767900328</v>
+        <v>0.05419219615246578</v>
       </c>
       <c r="F7" t="n">
-        <v>0.6324646883207158</v>
+        <v>0.6685478054594487</v>
       </c>
       <c r="G7" t="n">
         <v>0.05</v>
@@ -1587,19 +1614,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0.01572415130047658</v>
+        <v>-0.01391452100577122</v>
       </c>
       <c r="C8" t="n">
-        <v>0.03473873989641363</v>
+        <v>0.03582624135777856</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.08381083036575197</v>
+        <v>-0.08413266376845656</v>
       </c>
       <c r="E8" t="n">
-        <v>0.05236252776479881</v>
+        <v>0.05630362175691413</v>
       </c>
       <c r="F8" t="n">
-        <v>0.6508078233202111</v>
+        <v>0.697728122369965</v>
       </c>
       <c r="G8" t="n">
         <v>0.05</v>
@@ -1612,19 +1639,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-0.02773569665453215</v>
+        <v>-0.02606854715545239</v>
       </c>
       <c r="C9" t="n">
-        <v>0.03399195148821435</v>
+        <v>0.03445174256130683</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.09435869733566497</v>
+        <v>-0.09359272178025949</v>
       </c>
       <c r="E9" t="n">
-        <v>0.03888730402660066</v>
+        <v>0.04145562746935472</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4145293418323027</v>
+        <v>0.4492485122499703</v>
       </c>
       <c r="G9" t="n">
         <v>0.05</v>
@@ -1637,19 +1664,19 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-0.1239600656488278</v>
+        <v>-0.1243555105431011</v>
       </c>
       <c r="C10" t="n">
-        <v>0.05398652733054229</v>
+        <v>0.05548145045815731</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.229771714867078</v>
+        <v>-0.2330971552511327</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.01814841643057763</v>
+        <v>-0.01561386583506946</v>
       </c>
       <c r="F10" t="n">
-        <v>0.02166846993210025</v>
+        <v>0.0250008910074542</v>
       </c>
       <c r="G10" t="n">
         <v>0.05</v>
@@ -1662,19 +1689,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.07414605047067306</v>
+        <v>0.07368505338474868</v>
       </c>
       <c r="C11" t="n">
-        <v>0.05509860764353835</v>
+        <v>0.05628990533964618</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.03384523610896543</v>
+        <v>-0.03664113377412671</v>
       </c>
       <c r="E11" t="n">
-        <v>0.1821373370503115</v>
+        <v>0.1840112405436241</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1784001403301825</v>
+        <v>0.190524919365661</v>
       </c>
       <c r="G11" t="n">
         <v>0.05</v>
@@ -1687,19 +1714,19 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-0.05899078321978631</v>
+        <v>-0.0603922635557704</v>
       </c>
       <c r="C12" t="n">
-        <v>0.05639842925171484</v>
+        <v>0.06009378790448151</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.1695296733377777</v>
+        <v>-0.1781739235431429</v>
       </c>
       <c r="E12" t="n">
-        <v>0.05154810689820504</v>
+        <v>0.05738939643160208</v>
       </c>
       <c r="F12" t="n">
-        <v>0.2955771906625786</v>
+        <v>0.3149128220217325</v>
       </c>
       <c r="G12" t="n">
         <v>0.05</v>
@@ -1712,19 +1739,19 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-0.03955626422890936</v>
+        <v>-0.03918292931079818</v>
       </c>
       <c r="C13" t="n">
-        <v>0.05563255598453497</v>
+        <v>0.05709010836228827</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.1485940703265062</v>
+        <v>-0.1510774855743722</v>
       </c>
       <c r="E13" t="n">
-        <v>0.06948154186868741</v>
+        <v>0.07271162695277579</v>
       </c>
       <c r="F13" t="n">
-        <v>0.4770673392502235</v>
+        <v>0.4925019956822239</v>
       </c>
       <c r="G13" t="n">
         <v>0.05</v>
@@ -1737,19 +1764,19 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-0.08625988991259932</v>
+        <v>-0.08961924675638726</v>
       </c>
       <c r="C14" t="n">
-        <v>0.05632190850911778</v>
+        <v>0.05597301997478087</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.1966488021310302</v>
+        <v>-0.1993243500128988</v>
       </c>
       <c r="E14" t="n">
-        <v>0.02412902230583154</v>
+        <v>0.0200858565001243</v>
       </c>
       <c r="F14" t="n">
-        <v>0.1256332079941031</v>
+        <v>0.1093514311924689</v>
       </c>
       <c r="G14" t="n">
         <v>0.05</v>
@@ -1762,19 +1789,19 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-0.07934175362677316</v>
+        <v>-0.07971063832368426</v>
       </c>
       <c r="C15" t="n">
-        <v>0.05574038503364019</v>
+        <v>0.05486702563238855</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.1885909007771034</v>
+        <v>-0.1872480325020018</v>
       </c>
       <c r="E15" t="n">
-        <v>0.02990739352355706</v>
+        <v>0.02782675585463329</v>
       </c>
       <c r="F15" t="n">
-        <v>0.1546156087860307</v>
+        <v>0.1462801854677673</v>
       </c>
       <c r="G15" t="n">
         <v>0.05</v>
@@ -1787,19 +1814,19 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.07396866802185281</v>
+        <v>-0.07536173463392259</v>
       </c>
       <c r="C16" t="n">
-        <v>0.05454433721882339</v>
+        <v>0.05394309282729044</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.1808736045313543</v>
+        <v>-0.1810882537901128</v>
       </c>
       <c r="E16" t="n">
-        <v>0.03293626848764865</v>
+        <v>0.03036478452226758</v>
       </c>
       <c r="F16" t="n">
-        <v>0.175060982016161</v>
+        <v>0.1623955437074909</v>
       </c>
       <c r="G16" t="n">
         <v>0.05</v>
@@ -1812,19 +1839,19 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>-0.007513543301684525</v>
+        <v>-0.007508945504431082</v>
       </c>
       <c r="C17" t="n">
-        <v>0.05535990455848124</v>
+        <v>0.05689726041689014</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.1160169624238825</v>
+        <v>-0.1190255267405322</v>
       </c>
       <c r="E17" t="n">
-        <v>0.1009898758205135</v>
+        <v>0.10400763573167</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8920412503047446</v>
+        <v>0.8950050450910969</v>
       </c>
       <c r="G17" t="n">
         <v>0.05</v>
@@ -1837,19 +1864,19 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.02547115498824085</v>
+        <v>-0.02702123264755603</v>
       </c>
       <c r="C18" t="n">
-        <v>0.05422217118788809</v>
+        <v>0.05498884081168762</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.1317446576800669</v>
+        <v>-0.13479738019007</v>
       </c>
       <c r="E18" t="n">
-        <v>0.08080234770358521</v>
+        <v>0.08075491489495798</v>
       </c>
       <c r="F18" t="n">
-        <v>0.6385298181739003</v>
+        <v>0.6231472128909774</v>
       </c>
       <c r="G18" t="n">
         <v>0.05</v>
@@ -1862,19 +1889,19 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-0.08116365692003612</v>
+        <v>-0.08375751060329227</v>
       </c>
       <c r="C19" t="n">
-        <v>0.0545408555481829</v>
+        <v>0.0536099023493513</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.1880617694804762</v>
+        <v>-0.1888309884227301</v>
       </c>
       <c r="E19" t="n">
-        <v>0.02573445564040396</v>
+        <v>0.02131596721614551</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1367177079400226</v>
+        <v>0.1182052092143459</v>
       </c>
       <c r="G19" t="n">
         <v>0.05</v>
@@ -1887,19 +1914,19 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-0.1292857179043528</v>
+        <v>-0.1311358803541574</v>
       </c>
       <c r="C20" t="n">
-        <v>0.05414713559829628</v>
+        <v>0.05406282801340161</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.2354121535430202</v>
+        <v>-0.2370970761628077</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.02315928226568544</v>
+        <v>-0.02517468454550713</v>
       </c>
       <c r="F20" t="n">
-        <v>0.01695536584236703</v>
+        <v>0.01528225980615046</v>
       </c>
       <c r="G20" t="n">
         <v>0.05</v>
@@ -1912,19 +1939,19 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-0.1238930615488981</v>
+        <v>-0.1241875106822867</v>
       </c>
       <c r="C21" t="n">
-        <v>0.05496588966944551</v>
+        <v>0.05616362862747461</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.2316242256792136</v>
+        <v>-0.2342662000332196</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.01616189741858273</v>
+        <v>-0.01410882133135367</v>
       </c>
       <c r="F21" t="n">
-        <v>0.02419622951208942</v>
+        <v>0.02702384518809467</v>
       </c>
       <c r="G21" t="n">
         <v>0.05</v>
@@ -1937,19 +1964,19 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-0.07117739311407566</v>
+        <v>-0.07269691488818501</v>
       </c>
       <c r="C22" t="n">
-        <v>0.05753193130512074</v>
+        <v>0.05654139166683259</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.1839379064331448</v>
+        <v>-0.18351600619095</v>
       </c>
       <c r="E22" t="n">
-        <v>0.04158312020499345</v>
+        <v>0.03812217641457999</v>
       </c>
       <c r="F22" t="n">
-        <v>0.2160200174529999</v>
+        <v>0.1985376076796671</v>
       </c>
       <c r="G22" t="n">
         <v>0.05</v>
@@ -1962,19 +1989,19 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.0151312898172082</v>
+        <v>-0.01550704881921868</v>
       </c>
       <c r="C23" t="n">
-        <v>0.05292133363502843</v>
+        <v>0.05396301665233488</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.1188551977556921</v>
+        <v>-0.1212726179549302</v>
       </c>
       <c r="E23" t="n">
-        <v>0.0885926181212757</v>
+        <v>0.09025852031649288</v>
       </c>
       <c r="F23" t="n">
-        <v>0.7749390752177517</v>
+        <v>0.7738333321942777</v>
       </c>
       <c r="G23" t="n">
         <v>0.05</v>
@@ -1987,19 +2014,19 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-0.01627902621680755</v>
+        <v>-0.01712641609733919</v>
       </c>
       <c r="C24" t="n">
-        <v>0.04869486107156498</v>
+        <v>0.04898189205297216</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.1117192001492564</v>
+        <v>-0.1131291604157933</v>
       </c>
       <c r="E24" t="n">
-        <v>0.07916114771564131</v>
+        <v>0.07887632822111493</v>
       </c>
       <c r="F24" t="n">
-        <v>0.7381480126535398</v>
+        <v>0.7266029520031173</v>
       </c>
       <c r="G24" t="n">
         <v>0.05</v>
@@ -2012,19 +2039,19 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.01892643452517733</v>
+        <v>0.01900783443856896</v>
       </c>
       <c r="C25" t="n">
-        <v>0.0249478226082229</v>
+        <v>0.02561343601916736</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.02997039927963367</v>
+        <v>-0.03119357767932003</v>
       </c>
       <c r="E25" t="n">
-        <v>0.06782326832998833</v>
+        <v>0.06920924655645795</v>
       </c>
       <c r="F25" t="n">
-        <v>0.4480674969604823</v>
+        <v>0.4580243001316251</v>
       </c>
       <c r="G25" t="n">
         <v>0.05</v>
@@ -2037,19 +2064,19 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.01021551331248089</v>
+        <v>-0.0114178392397319</v>
       </c>
       <c r="C26" t="n">
-        <v>0.03126959165356898</v>
+        <v>0.03075125430929366</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.07150278676475036</v>
+        <v>-0.07168919016537961</v>
       </c>
       <c r="E26" t="n">
-        <v>0.05107176013978858</v>
+        <v>0.04885351168591581</v>
       </c>
       <c r="F26" t="n">
-        <v>0.7439011449059137</v>
+        <v>0.7104165557437969</v>
       </c>
       <c r="G26" t="n">
         <v>0.05</v>
@@ -2062,19 +2089,19 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.008039595893816476</v>
+        <v>0.008263771382752895</v>
       </c>
       <c r="C27" t="n">
-        <v>0.0311149108042966</v>
+        <v>0.03117627639559386</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.05294450866478106</v>
+        <v>-0.05284060752467729</v>
       </c>
       <c r="E27" t="n">
-        <v>0.06902370045241402</v>
+        <v>0.06936815029018308</v>
       </c>
       <c r="F27" t="n">
-        <v>0.7961105442515402</v>
+        <v>0.7909586063851299</v>
       </c>
       <c r="G27" t="n">
         <v>0.05</v>
@@ -2087,19 +2114,19 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.04425270479025433</v>
+        <v>0.0441132339242141</v>
       </c>
       <c r="C28" t="n">
-        <v>0.03127430413289793</v>
+        <v>0.03148338007871244</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.01704380495177778</v>
+        <v>-0.0175930571416481</v>
       </c>
       <c r="E28" t="n">
-        <v>0.1055492145322864</v>
+        <v>0.1058195249900763</v>
       </c>
       <c r="F28" t="n">
-        <v>0.1570725794615354</v>
+        <v>0.1611664122763743</v>
       </c>
       <c r="G28" t="n">
         <v>0.05</v>
@@ -2112,19 +2139,19 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.009637889703426996</v>
+        <v>-0.0109349089395617</v>
       </c>
       <c r="C29" t="n">
-        <v>0.03168024999645823</v>
+        <v>0.03231638714325723</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.0717300387177103</v>
+        <v>-0.07427386385079912</v>
       </c>
       <c r="E29" t="n">
-        <v>0.05245425931085631</v>
+        <v>0.05240404597167572</v>
       </c>
       <c r="F29" t="n">
-        <v>0.76095730574406</v>
+        <v>0.7350840751185987</v>
       </c>
       <c r="G29" t="n">
         <v>0.05</v>
@@ -2137,19 +2164,19 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.2311650223435082</v>
+        <v>0.2300267851900341</v>
       </c>
       <c r="C30" t="n">
-        <v>0.04307563847579732</v>
+        <v>0.04275687264023308</v>
       </c>
       <c r="D30" t="n">
-        <v>0.1467383223198777</v>
+        <v>0.1462248547236112</v>
       </c>
       <c r="E30" t="n">
-        <v>0.3155917223671388</v>
+        <v>0.3138287156564569</v>
       </c>
       <c r="F30" t="n">
-        <v>8.028324442825778e-08</v>
+        <v>7.453607464503556e-08</v>
       </c>
       <c r="G30" t="n">
         <v>0.05</v>
@@ -2158,23 +2185,23 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>team_size</t>
+          <t>baseline_turnover_intention</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.008827564436029833</v>
+        <v>0.4906715993267194</v>
       </c>
       <c r="C31" t="n">
-        <v>0.004267040038873769</v>
+        <v>0.01020038761332359</v>
       </c>
       <c r="D31" t="n">
-        <v>0.0004643196392468546</v>
+        <v>0.4706792069762566</v>
       </c>
       <c r="E31" t="n">
-        <v>0.01719080923281281</v>
+        <v>0.5106639916771821</v>
       </c>
       <c r="F31" t="n">
-        <v>0.03856679446568418</v>
+        <v>0</v>
       </c>
       <c r="G31" t="n">
         <v>0.05</v>
@@ -2183,23 +2210,23 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>baseline_turnover_intention</t>
+          <t>tenure_months</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.491360234616454</v>
+        <v>-0.001002562195601323</v>
       </c>
       <c r="C32" t="n">
-        <v>0.009998215349491885</v>
+        <v>0.001411716497337638</v>
       </c>
       <c r="D32" t="n">
-        <v>0.4717640926217744</v>
+        <v>-0.003769475686764128</v>
       </c>
       <c r="E32" t="n">
-        <v>0.5109563766111337</v>
+        <v>0.001764351295561482</v>
       </c>
       <c r="F32" t="n">
-        <v>0</v>
+        <v>0.4775971888880661</v>
       </c>
       <c r="G32" t="n">
         <v>0.05</v>
@@ -2212,19 +2239,19 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.0008338932702891721</v>
+        <v>-0.0008959807646594347</v>
       </c>
       <c r="C33" t="n">
-        <v>0.001755670457749581</v>
+        <v>0.001756049857289183</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.004274944136199302</v>
+        <v>-0.004337775240002936</v>
       </c>
       <c r="E33" t="n">
-        <v>0.002607157595620958</v>
+        <v>0.002545813710684066</v>
       </c>
       <c r="F33" t="n">
-        <v>0.634807352389672</v>
+        <v>0.6098937492520402</v>
       </c>
       <c r="G33" t="n">
         <v>0.05</v>
@@ -2233,23 +2260,23 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>tenure_months</t>
+          <t>num_direct_reports</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.001082238627225144</v>
+        <v>-0.007701111887135871</v>
       </c>
       <c r="C34" t="n">
-        <v>0.00147232832246986</v>
+        <v>0.004563797415138302</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.003967949112684345</v>
+        <v>-0.01664599045354394</v>
       </c>
       <c r="E34" t="n">
-        <v>0.001803471858234057</v>
+        <v>0.001243766679272195</v>
       </c>
       <c r="F34" t="n">
-        <v>0.4623075158120994</v>
+        <v>0.09151972193447906</v>
       </c>
       <c r="G34" t="n">
         <v>0.05</v>
@@ -2262,21 +2289,46 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.008363563237803323</v>
+        <v>0.009570099507611842</v>
       </c>
       <c r="C35" t="n">
-        <v>0.02380633314767729</v>
+        <v>0.02352815839717278</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.03829599233560622</v>
+        <v>-0.03654424357340046</v>
       </c>
       <c r="E35" t="n">
-        <v>0.05502311881121286</v>
+        <v>0.05568444258862414</v>
       </c>
       <c r="F35" t="n">
-        <v>0.7253507412814979</v>
+        <v>0.6841909551554406</v>
       </c>
       <c r="G35" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>tot_span_of_control</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>0.001336822150411828</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0.001449434599930922</v>
+      </c>
+      <c r="D36" t="n">
+        <v>-0.001504017463399</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.004177661764222657</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0.356369013200117</v>
+      </c>
+      <c r="G36" t="n">
         <v>0.05</v>
       </c>
     </row>
@@ -2291,7 +2343,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D33"/>
+  <dimension ref="A1:D34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2323,13 +2375,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-2.424595366175215</v>
+        <v>-2.680600179802938</v>
       </c>
       <c r="C2" t="n">
-        <v>0.4699812973694731</v>
+        <v>0.4771933030981325</v>
       </c>
       <c r="D2" t="n">
-        <v>2.483799515165129e-07</v>
+        <v>1.938181768271168e-08</v>
       </c>
     </row>
     <row r="3">
@@ -2339,13 +2391,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.02313926327040559</v>
+        <v>-0.02542074333516161</v>
       </c>
       <c r="C3" t="n">
-        <v>0.09767081015513708</v>
+        <v>0.1002143663033997</v>
       </c>
       <c r="D3" t="n">
-        <v>0.8127260429188259</v>
+        <v>0.79975540801217</v>
       </c>
     </row>
     <row r="4">
@@ -2355,13 +2407,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.2234052412627192</v>
+        <v>0.2244463748843409</v>
       </c>
       <c r="C4" t="n">
-        <v>0.2328794775545217</v>
+        <v>0.2335027157442914</v>
       </c>
       <c r="D4" t="n">
-        <v>0.3373990748904945</v>
+        <v>0.3364439424069159</v>
       </c>
     </row>
     <row r="5">
@@ -2371,13 +2423,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.8180627404127299</v>
+        <v>0.8155080917228588</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1689953683152051</v>
+        <v>0.1734026513921177</v>
       </c>
       <c r="D5" t="n">
-        <v>1.293561359606461e-06</v>
+        <v>2.563995828054277e-06</v>
       </c>
     </row>
     <row r="6">
@@ -2387,13 +2439,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.03544498749496686</v>
+        <v>0.03527526670387295</v>
       </c>
       <c r="C6" t="n">
-        <v>0.1931765738941879</v>
+        <v>0.191688294691954</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8544175529024153</v>
+        <v>0.853994545471355</v>
       </c>
     </row>
     <row r="7">
@@ -2403,13 +2455,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.275906022416754</v>
+        <v>0.2773648159307716</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1812662634417183</v>
+        <v>0.1901447102133382</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1279831375553563</v>
+        <v>0.1446466431125516</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2471,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1078851505724593</v>
+        <v>0.1036811851537241</v>
       </c>
       <c r="C8" t="n">
-        <v>0.1932040242209362</v>
+        <v>0.1952515666982443</v>
       </c>
       <c r="D8" t="n">
-        <v>0.576571189971413</v>
+        <v>0.5954095400432464</v>
       </c>
     </row>
     <row r="9">
@@ -2435,13 +2487,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.871778570870576</v>
+        <v>0.8738774480300985</v>
       </c>
       <c r="C9" t="n">
-        <v>0.1678649218702299</v>
+        <v>0.1695280942409136</v>
       </c>
       <c r="D9" t="n">
-        <v>2.065613561488396e-07</v>
+        <v>2.539495077342701e-07</v>
       </c>
     </row>
     <row r="10">
@@ -2451,13 +2503,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-0.037352240367789</v>
+        <v>-0.04456520772617086</v>
       </c>
       <c r="C10" t="n">
-        <v>0.2698916813503851</v>
+        <v>0.2604021031716313</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8899265467947022</v>
+        <v>0.8641137091517834</v>
       </c>
     </row>
     <row r="11">
@@ -2467,13 +2519,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-0.2713985237416621</v>
+        <v>-0.2737623724798149</v>
       </c>
       <c r="C11" t="n">
-        <v>0.2816070653033665</v>
+        <v>0.2787881385465057</v>
       </c>
       <c r="D11" t="n">
-        <v>0.3351717882228968</v>
+        <v>0.3261132423877617</v>
       </c>
     </row>
     <row r="12">
@@ -2483,13 +2535,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.08472740319905862</v>
+        <v>0.08100487957118127</v>
       </c>
       <c r="C12" t="n">
-        <v>0.258092362680186</v>
+        <v>0.2596429772097166</v>
       </c>
       <c r="D12" t="n">
-        <v>0.7426974971355069</v>
+        <v>0.7550514391424692</v>
       </c>
     </row>
     <row r="13">
@@ -2499,13 +2551,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.04068301518422479</v>
+        <v>0.03917827337461736</v>
       </c>
       <c r="C13" t="n">
-        <v>0.2611004784975071</v>
+        <v>0.2572958805743769</v>
       </c>
       <c r="D13" t="n">
-        <v>0.8761799211234182</v>
+        <v>0.8789745077123745</v>
       </c>
     </row>
     <row r="14">
@@ -2515,13 +2567,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-0.05345693884495933</v>
+        <v>-0.05296103812307947</v>
       </c>
       <c r="C14" t="n">
-        <v>0.2638638610262009</v>
+        <v>0.2610089865588713</v>
       </c>
       <c r="D14" t="n">
-        <v>0.8394532575785491</v>
+        <v>0.8392062624375523</v>
       </c>
     </row>
     <row r="15">
@@ -2531,13 +2583,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.1239335042277773</v>
+        <v>0.1181322726534159</v>
       </c>
       <c r="C15" t="n">
-        <v>0.25992806241409</v>
+        <v>0.2572294350577177</v>
       </c>
       <c r="D15" t="n">
-        <v>0.6335050825508384</v>
+        <v>0.646055612898408</v>
       </c>
     </row>
     <row r="16">
@@ -2547,13 +2599,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.001862882312141687</v>
+        <v>-0.004000986240379581</v>
       </c>
       <c r="C16" t="n">
-        <v>0.2575901907586843</v>
+        <v>0.2383903410311186</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9942297799667277</v>
+        <v>0.9866094604655129</v>
       </c>
     </row>
     <row r="17">
@@ -2563,13 +2615,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.1116424378426662</v>
+        <v>0.1057185310395304</v>
       </c>
       <c r="C17" t="n">
-        <v>0.2586555011338381</v>
+        <v>0.2543340222421748</v>
       </c>
       <c r="D17" t="n">
-        <v>0.6660132626676296</v>
+        <v>0.6776529122567303</v>
       </c>
     </row>
     <row r="18">
@@ -2579,13 +2631,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.1317171712348868</v>
+        <v>-0.1377694895733256</v>
       </c>
       <c r="C18" t="n">
-        <v>0.2668604874679544</v>
+        <v>0.2636874203313626</v>
       </c>
       <c r="D18" t="n">
-        <v>0.6216023734866079</v>
+        <v>0.6013412201546261</v>
       </c>
     </row>
     <row r="19">
@@ -2595,13 +2647,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-0.02274331928780688</v>
+        <v>-0.02557154094223238</v>
       </c>
       <c r="C19" t="n">
-        <v>0.2635260713514327</v>
+        <v>0.252759790153811</v>
       </c>
       <c r="D19" t="n">
-        <v>0.9312248636975232</v>
+        <v>0.9194160355966675</v>
       </c>
     </row>
     <row r="20">
@@ -2611,13 +2663,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-0.06665392434463961</v>
+        <v>-0.07344622569376427</v>
       </c>
       <c r="C20" t="n">
-        <v>0.265659520794061</v>
+        <v>0.267457860954101</v>
       </c>
       <c r="D20" t="n">
-        <v>0.8018915682492664</v>
+        <v>0.7836169672222772</v>
       </c>
     </row>
     <row r="21">
@@ -2627,13 +2679,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.2096018965396373</v>
+        <v>0.2063167170305059</v>
       </c>
       <c r="C21" t="n">
-        <v>0.2485899459155399</v>
+        <v>0.244289653245072</v>
       </c>
       <c r="D21" t="n">
-        <v>0.3991371714945826</v>
+        <v>0.3983578134719846</v>
       </c>
     </row>
     <row r="22">
@@ -2643,13 +2695,13 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-0.1668969509214496</v>
+        <v>-0.1704634573362026</v>
       </c>
       <c r="C22" t="n">
-        <v>0.2747515009079846</v>
+        <v>0.2696748454965904</v>
       </c>
       <c r="D22" t="n">
-        <v>0.5435543635085022</v>
+        <v>0.5273167196806361</v>
       </c>
     </row>
     <row r="23">
@@ -2659,13 +2711,13 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.4971940641810814</v>
+        <v>-0.5008110927334757</v>
       </c>
       <c r="C23" t="n">
-        <v>0.2924423511374601</v>
+        <v>0.287067218044571</v>
       </c>
       <c r="D23" t="n">
-        <v>0.08910387128184533</v>
+        <v>0.08105838975171785</v>
       </c>
     </row>
     <row r="24">
@@ -2675,13 +2727,13 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.939948370751521</v>
+        <v>0.9366864721074267</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1570978378415049</v>
+        <v>0.1483430409733375</v>
       </c>
       <c r="D24" t="n">
-        <v>2.187908098302239e-09</v>
+        <v>2.713396260923891e-10</v>
       </c>
     </row>
     <row r="25">
@@ -2691,13 +2743,13 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-0.5774584503453005</v>
+        <v>-0.5776106069409677</v>
       </c>
       <c r="C25" t="n">
-        <v>0.1153148485868671</v>
+        <v>0.1143619392421807</v>
       </c>
       <c r="D25" t="n">
-        <v>5.50935246170832e-07</v>
+        <v>4.401383208103943e-07</v>
       </c>
     </row>
     <row r="26">
@@ -2707,13 +2759,13 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.2375989005820144</v>
+        <v>0.237316144844174</v>
       </c>
       <c r="C26" t="n">
-        <v>0.1483942012834082</v>
+        <v>0.1503781926377478</v>
       </c>
       <c r="D26" t="n">
-        <v>0.1093473930483596</v>
+        <v>0.1145360411757813</v>
       </c>
     </row>
     <row r="27">
@@ -2723,13 +2775,13 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.04390400011939626</v>
+        <v>-0.04350476117998651</v>
       </c>
       <c r="C27" t="n">
-        <v>0.1581709974635947</v>
+        <v>0.1611879340386412</v>
       </c>
       <c r="D27" t="n">
-        <v>0.7813401518906566</v>
+        <v>0.7872365295400213</v>
       </c>
     </row>
     <row r="28">
@@ -2739,13 +2791,13 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.07706864556787009</v>
+        <v>-0.07514354096975732</v>
       </c>
       <c r="C28" t="n">
-        <v>0.1578050341313147</v>
+        <v>0.1613683918223567</v>
       </c>
       <c r="D28" t="n">
-        <v>0.6252814998540484</v>
+        <v>0.6414556246120151</v>
       </c>
     </row>
     <row r="29">
@@ -2755,29 +2807,29 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.09735884295377209</v>
+        <v>0.09749293462742097</v>
       </c>
       <c r="C29" t="n">
-        <v>0.1528329758433737</v>
+        <v>0.1543265796290165</v>
       </c>
       <c r="D29" t="n">
-        <v>0.5241067842939673</v>
+        <v>0.5275624553510008</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>team_size</t>
+          <t>tenure_months</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.0214099884697233</v>
+        <v>-0.002418133412192873</v>
       </c>
       <c r="C30" t="n">
-        <v>0.02125751820946937</v>
+        <v>0.007135781003458546</v>
       </c>
       <c r="D30" t="n">
-        <v>0.3138518697701007</v>
+        <v>0.7347043603418277</v>
       </c>
     </row>
     <row r="31">
@@ -2787,29 +2839,29 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.004963851467081969</v>
+        <v>-0.005012017390962195</v>
       </c>
       <c r="C31" t="n">
-        <v>0.008295015527615652</v>
+        <v>0.008304876992455039</v>
       </c>
       <c r="D31" t="n">
-        <v>0.5495638837811058</v>
+        <v>0.5461741835341576</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>tenure_months</t>
+          <t>num_direct_reports</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.002369150025834419</v>
+        <v>-0.004129656026475419</v>
       </c>
       <c r="C32" t="n">
-        <v>0.007250684388774151</v>
+        <v>0.02222260881033174</v>
       </c>
       <c r="D32" t="n">
-        <v>0.7438581373219401</v>
+        <v>0.8525770672961279</v>
       </c>
     </row>
     <row r="33">
@@ -2819,13 +2871,29 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.228992117455078</v>
+        <v>0.2280638724458785</v>
       </c>
       <c r="C33" t="n">
-        <v>0.1106079911201261</v>
+        <v>0.1146565719927948</v>
       </c>
       <c r="D33" t="n">
-        <v>0.03842392670187963</v>
+        <v>0.04668969945129923</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>tot_span_of_control</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>0.006335499136474495</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0.006871422968197181</v>
+      </c>
+      <c r="D34" t="n">
+        <v>0.3565249957666435</v>
       </c>
     </row>
   </sheetData>
